--- a/sampleprojects/CorporateTax/excel/states/MD_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/MD_corp.xlsx
@@ -70,7 +70,7 @@
     <t>Meets economic nexus threshold ($100K gross receipts); result.md_gross_receipts is greater than or equal to result.md_economic_nexus_threshold</t>
   </si>
   <si>
-    <t>result.md_gross_receipts &gt;= result.md_economic_nexus_threshold</t>
+    <t>md_result.gross_receipts &gt;= md_result.economic_nexus_threshold</t>
   </si>
   <si>
     <t>-</t>
@@ -85,7 +85,7 @@
     <t>Physical nexus - filing required</t>
   </si>
   <si>
-    <t>set result.md_has_nexus = true;</t>
+    <t>set md_result.has_nexus = true;</t>
   </si>
   <si>
     <t>X</t>
@@ -97,7 +97,7 @@
     <t>No nexus - no filing required</t>
   </si>
   <si>
-    <t>set result.md_has_nexus = false; set result.md_tax_liability = 0.0;</t>
+    <t>set md_result.has_nexus = false; set md_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate MD Income Adjustments</t>
@@ -115,19 +115,19 @@
     <t>Has Maryland nexus</t>
   </si>
   <si>
-    <t>result.md_has_nexus is equal to true</t>
+    <t>md_result.has_nexus is equal to true</t>
   </si>
   <si>
     <t>Calculate Maryland state additions and subtractions; Calculate state-specific income adjustments</t>
   </si>
   <si>
-    <t>set result.md_state_additions = 0.0; if result.md_us_interest_income != 0.0 then set result.md_state_additions = result.md_state_additions + result.md_us_interest_income; endif set result.md_state_subtractions = 0.0; if result.md_municipal_interest != 0.0 then set result.md_state_subtractions = result.md_state_subtractions + result.md_municipal_interest; endif add (("Maryland additions: $" + string value of (result.md_state_additions)) + ", subtractions: $") + string value of (result.md_state_subtractions) to job.audit_trail;</t>
+    <t>set md_result.state_additions = 0.0; if md_result.us_interest_income != 0.0 then set md_result.state_additions = md_result.state_additions + md_result.us_interest_income; endif set md_result.state_subtractions = 0.0; if md_result.municipal_interest != 0.0 then set md_result.state_subtractions = md_result.state_subtractions + md_result.municipal_interest; endif add (("Maryland additions: $" + string value of (md_result.state_additions)) + ", subtractions: $") + string value of (md_result.state_subtractions) to job.audit_trail;</t>
   </si>
   <si>
     <t>No nexus - no adjustments</t>
   </si>
   <si>
-    <t>set result.md_state_additions = 0.0; set result.md_state_subtractions = 0.0;</t>
+    <t>set md_result.state_additions = 0.0; set md_result.state_subtractions = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate MD State Tax</t>
@@ -145,19 +145,19 @@
     <t>Has positive taxable income; result.md_apportioned_income is greater than 0</t>
   </si>
   <si>
-    <t>result.md_apportioned_income &gt; 0.0</t>
+    <t>md_result.apportioned_income &gt; 0.0</t>
   </si>
   <si>
     <t>Calculate Maryland corporate tax (flat rate 8.25%); Apply Maryland 8.25% flat rate</t>
   </si>
   <si>
-    <t>set result.md_taxable_income = the maximum of (result.md_apportioned_income + result.md_state_additions - result.md_state_subtractions) and (0.0); set result.md_tax_liability = the maximum of (result.md_taxable_income * result.md_corp_tax_rate - result.md_state_credits) and (0.0); set result.md_refund_or_owed = result.md_estimated_payments - result.md_tax_liability; add "Maryland taxable income: $" + string value of (result.md_taxable_income) to job.audit_trail; add "Maryland tax liability (8.25%): $" + string value of (result.md_tax_liability) to job.audit_trail;</t>
+    <t>set md_result.taxable_income = the maximum of (md_result.apportioned_income + md_result.state_additions - md_result.state_subtractions) and (0.0); set md_result.tax_liability = the maximum of (md_result.taxable_income * md_result.corp_tax_rate - md_result.state_credits) and (0.0); set md_result.refund_or_owed = md_result.estimated_payments - md_result.tax_liability; add "Maryland taxable income: $" + string value of (md_result.taxable_income) to job.audit_trail; add "Maryland tax liability (8.25%): $" + string value of (md_result.tax_liability) to job.audit_trail;</t>
   </si>
   <si>
     <t>No taxable income - no tax liability</t>
   </si>
   <si>
-    <t>set result.md_taxable_income = 0.0; set result.md_tax_liability = 0.0;</t>
+    <t>set md_result.taxable_income = 0.0; set md_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>No nexus - no tax liability</t>
@@ -205,13 +205,13 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>result</t>
+    <t>md_result</t>
   </si>
   <si>
     <t>(16 attributes)</t>
   </si>
   <si>
-    <t>md_apportioned_income</t>
+    <t>apportioned_income</t>
   </si>
   <si>
     <t>double</t>
@@ -226,7 +226,7 @@
     <t>Declared from decision-table usage; referenced by MD but never declared (campaign #948 Phase 1)</t>
   </si>
   <si>
-    <t>md_apportionment_formula</t>
+    <t>apportionment_formula</t>
   </si>
   <si>
     <t>string</t>
@@ -238,7 +238,7 @@
     <t>MD uses single-sales factor apportionment (100% sales)</t>
   </si>
   <si>
-    <t>md_corp_tax_rate</t>
+    <t>corp_tax_rate</t>
   </si>
   <si>
     <t>0.0825</t>
@@ -247,7 +247,7 @@
     <t>MD corporate income tax rate - 8.25% flat rate (MD Tax-General Code § 10-105)</t>
   </si>
   <si>
-    <t>md_economic_nexus_threshold</t>
+    <t>economic_nexus_threshold</t>
   </si>
   <si>
     <t>100000.0</t>
@@ -256,13 +256,13 @@
     <t>MD economic nexus threshold - $100,000 gross receipts</t>
   </si>
   <si>
-    <t>md_estimated_payments</t>
-  </si>
-  <si>
-    <t>md_gross_receipts</t>
-  </si>
-  <si>
-    <t>md_has_nexus</t>
+    <t>estimated_payments</t>
+  </si>
+  <si>
+    <t>gross_receipts</t>
+  </si>
+  <si>
+    <t>has_nexus</t>
   </si>
   <si>
     <t>boolean</t>
@@ -271,37 +271,37 @@
     <t>false</t>
   </si>
   <si>
-    <t>md_municipal_interest</t>
-  </si>
-  <si>
-    <t>md_refund_or_owed</t>
-  </si>
-  <si>
-    <t>md_state_additions</t>
+    <t>municipal_interest</t>
+  </si>
+  <si>
+    <t>refund_or_owed</t>
+  </si>
+  <si>
+    <t>state_additions</t>
   </si>
   <si>
     <t>MD-specific additions: federal interest, state tax refunds, bonus depreciation addback, etc.</t>
   </si>
   <si>
-    <t>md_state_credits</t>
+    <t>state_credits</t>
   </si>
   <si>
     <t>MD tax credits: R&amp;D, job creation, biotechnology investment, etc.</t>
   </si>
   <si>
-    <t>md_state_subtractions</t>
+    <t>state_subtractions</t>
   </si>
   <si>
     <t>MD-specific subtractions: municipal interest, NOL modifications, etc.</t>
   </si>
   <si>
-    <t>md_tax_liability</t>
-  </si>
-  <si>
-    <t>md_taxable_income</t>
-  </si>
-  <si>
-    <t>md_transaction_threshold</t>
+    <t>tax_liability</t>
+  </si>
+  <si>
+    <t>taxable_income</t>
+  </si>
+  <si>
+    <t>transaction_threshold</t>
   </si>
   <si>
     <t>integer</t>
@@ -313,7 +313,7 @@
     <t>MD economic nexus transaction count threshold - 200 transactions</t>
   </si>
   <si>
-    <t>md_us_interest_income</t>
+    <t>us_interest_income</t>
   </si>
 </sst>
 </file>
